--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92575631981</v>
+        <v>46157.93120224086</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93120224086</v>
+        <v>46157.93186131955</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93186131955</v>
+        <v>46157.93407011421</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93407011421</v>
+        <v>46157.9372511745</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9372511745</v>
+        <v>46158.28222668308</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28222668308</v>
+        <v>46158.29710843094</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29710843094</v>
+        <v>46158.29822687615</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29822687615</v>
+        <v>46158.33393638123</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33393638123</v>
+        <v>46158.36863420243</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36863420243</v>
+        <v>46158.3729439391</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
